--- a/public/templates/TDS_Data_Entry_Client_Template.xlsx
+++ b/public/templates/TDS_Data_Entry_Client_Template.xlsx
@@ -39,7 +39,7 @@
     <t>One Challan can have MANY TDS Entries linked to it. Many entries can share the same Challan ID.</t>
   </si>
   <si>
-    <t>Row 4 on both sheets is a WORKED EXAMPLE, shown in gray — delete or overwrite it before submitting; it exists only to show the expected format.</t>
+    <t>Row 4 on both sheets is a WORKED EXAMPLE, shown in gray. You may delete it, overwrite it, or simply leave it — the software recognises its Challan ID (EXAMPLE-DO-NOT-IMPORT) and always excludes that row from import, so it can never end up in your real data.</t>
   </si>
   <si>
     <t>Yellow-shaded cells are where you enter data. Green-shaded cells calculate automatically — do not type into them.</t>
@@ -201,10 +201,10 @@
     <t>CHALLAN DETAILS  —  one row per TDS challan deposited</t>
   </si>
   <si>
-    <t>Row 4 (gray) is a worked example — delete or overwrite before submitting.</t>
+    <t>Row 4 (gray) is a worked example — its Challan ID (EXAMPLE-DO-NOT-IMPORT) is auto-excluded on import, so delete it, overwrite it, or leave it as-is.</t>
   </si>
   <si>
-    <t>CH-001</t>
+    <t>EXAMPLE-DO-NOT-IMPORT</t>
   </si>
   <si>
     <t>0510002</t>
@@ -1104,7 +1104,8 @@
   <dimension ref="A1:I204"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="2" width="14" customWidth="1"/>
+    <col min="1" max="1" width="24" customWidth="1"/>
+    <col min="2" max="2" width="14" customWidth="1"/>
     <col min="3" max="4" width="16" customWidth="1"/>
     <col min="5" max="5" width="20" customWidth="1"/>
     <col min="6" max="6" width="16" customWidth="1"/>
@@ -4218,7 +4219,7 @@
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
-    <col min="2" max="2" width="12" customWidth="1"/>
+    <col min="2" max="2" width="24" customWidth="1"/>
     <col min="3" max="3" width="26" customWidth="1"/>
     <col min="4" max="4" width="13" customWidth="1"/>
     <col min="5" max="5" width="10" customWidth="1"/>
